--- a/wiki/reports/daily/2026-09-30_일일보고.xlsx
+++ b/wiki/reports/daily/2026-09-30_일일보고.xlsx
@@ -76,7 +76,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -95,12 +95,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FADBD8"/>
+        <fgColor rgb="00D5F5E3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FADBD8"/>
       </patternFill>
     </fill>
     <fill>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -185,19 +190,25 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -209,10 +220,10 @@
     <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -613,7 +624,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성: 2026-09-30 07:56   |   전일: 9월 29일   |   월평균 기준: 이전 작업일 19일 평균   |   9월 누적 작업일: 20일</t>
+          <t>생성: 2026-09-30 16:00   |   전일: 9월 29일   |   월평균 기준: 이전 작업일 19일 평균   |   9월 누적 작업일: 20일</t>
         </is>
       </c>
     </row>
@@ -675,25 +686,25 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="C4" s="6" t="n">
         <v>33</v>
       </c>
       <c r="D4" s="7" t="n">
-        <v>-8</v>
+        <v>32</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>-0.2424242424242424</v>
+        <v>0.9696969696969697</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>29.9</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>-4.94736842105263</v>
+        <v>35.05263157894737</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>-0.1652021089630931</v>
+        <v>1.170474516695958</v>
       </c>
       <c r="I4" s="10" t="inlineStr"/>
     </row>
@@ -704,29 +715,29 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>5900</v>
+        <v>13686</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>7354</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>-1454</v>
+        <v>6332</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>-0.1977155289638292</v>
+        <v>0.8610280119662769</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>7470.5</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>-1570.473684210527</v>
+        <v>6215.526315789473</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>-0.2102241103572662</v>
+        <v>0.8320123433305856</v>
       </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
-          <t>1:38:20</t>
+          <t>3:48:06</t>
         </is>
       </c>
     </row>
@@ -737,25 +748,25 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>35</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>-20</v>
+        <v>1</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>-0.5714285714285714</v>
+        <v>0.02857142857142857</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>-5.526315789473685</v>
+        <v>15.36842105263158</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>-0.2692307692307693</v>
+        <v>0.7448979591836734</v>
       </c>
       <c r="I6" s="10" t="inlineStr"/>
     </row>
@@ -766,143 +777,143 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>6225</v>
+        <v>11584</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>11691</v>
       </c>
-      <c r="D7" s="7" t="n">
-        <v>-5466</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>-0.4675391326661534</v>
+      <c r="D7" s="12" t="n">
+        <v>-107</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>-0.009152339406380976</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>7401.1</v>
+        <v>7430.8</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>-1176.105263157895</v>
+        <v>4153.210526315789</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>-0.1589094089787443</v>
+        <v>0.5589191486347699</v>
       </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
-          <t>1:43:45</t>
+          <t>3:13:04</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>합계  수량 (개)</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>68</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>-28</v>
+        <v>33</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>-0.4117647058823529</v>
+        <v>0.4852941176470588</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>-10.47368421052632</v>
+        <v>50.42105263157895</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>-0.2075078206465068</v>
+        <v>0.9968782518210196</v>
       </c>
       <c r="I8" s="10" t="inlineStr"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
         <is>
           <t>합계  가공시간 (초)</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>12125</v>
+        <v>25270</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>19045</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>-6920</v>
+        <v>6225</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>-0.3633499606195852</v>
+        <v>0.3268574428983985</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>14871.6</v>
+        <v>14901.3</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-2746.578947368422</v>
+        <v>10368.73684210526</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>-0.1846864382785957</v>
+        <v>0.695829389242876</v>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>3:22:05</t>
+          <t>7:01:10</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>합계  금액</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>63</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>-23</v>
+        <v>38</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>-0.3650793650793651</v>
+        <v>0.6031746031746031</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>-9.526315789473685</v>
+        <v>51.36842105263158</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>-0.1923485653560043</v>
+        <v>1.034994697773065</v>
       </c>
       <c r="I10" s="10" t="inlineStr"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>9월 누적  (20일 / 30일 중 작업일)</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="14" t="n">
-        <v>999</v>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>294685</v>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>981</v>
-      </c>
-      <c r="F11" s="13" t="n"/>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="13" t="n"/>
-      <c r="I11" s="13" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="16" t="n">
+        <v>1062</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>308394</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>1044</v>
+      </c>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="15" t="n"/>
+      <c r="H11" s="15" t="n"/>
+      <c r="I11" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -920,7 +931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -944,272 +955,518 @@
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>■ FAST GRIND</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>형상</t>
         </is>
       </c>
-      <c r="C3" s="16" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>날수(F)</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="D3" s="18" t="inlineStr">
         <is>
           <t>날경(Ø)</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
+      <c r="E3" s="18" t="inlineStr">
         <is>
           <t>상크경(Ø)</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="F3" s="18" t="inlineStr">
         <is>
           <t>코팅</t>
         </is>
       </c>
-      <c r="G3" s="16" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>특이사항</t>
         </is>
       </c>
-      <c r="H3" s="16" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I3" s="16" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>수량(개)</t>
         </is>
       </c>
-      <c r="J3" s="16" t="inlineStr">
+      <c r="J3" s="18" t="inlineStr">
         <is>
           <t>시간합계(초)</t>
         </is>
       </c>
-      <c r="K3" s="16" t="inlineStr">
+      <c r="K3" s="18" t="inlineStr">
         <is>
           <t>시간(H:M:S)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="17" t="n">
+      <c r="A4" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>볼</t>
         </is>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="17" t="n">
+      <c r="D4" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="E4" s="17" t="n">
+      <c r="E4" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>뮤</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
+      <c r="G4" s="20" t="inlineStr">
         <is>
           <t>0107</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr"/>
-      <c r="I4" s="19" t="n">
+      <c r="H4" s="19" t="inlineStr"/>
+      <c r="I4" s="21" t="n">
         <v>25</v>
       </c>
-      <c r="J4" s="19" t="n">
+      <c r="J4" s="21" t="n">
         <v>5900</v>
       </c>
-      <c r="K4" s="17" t="inlineStr">
+      <c r="K4" s="19" t="inlineStr">
         <is>
           <t>1:38:20</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>R0.5</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>0107 ㅋㅌ</t>
+        </is>
+      </c>
+      <c r="H5" s="19" t="inlineStr"/>
+      <c r="I5" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="J5" s="21" t="n">
+        <v>1576</v>
+      </c>
+      <c r="K5" s="19" t="inlineStr">
+        <is>
+          <t>0:26:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>0107</t>
+        </is>
+      </c>
+      <c r="H6" s="19" t="inlineStr"/>
+      <c r="I6" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="21" t="n">
+        <v>300</v>
+      </c>
+      <c r="K6" s="19" t="inlineStr">
+        <is>
+          <t>0:05:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>뮤</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>0068</t>
+        </is>
+      </c>
+      <c r="H7" s="19" t="inlineStr"/>
+      <c r="I7" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="J7" s="21" t="n">
+        <v>5910</v>
+      </c>
+      <c r="K7" s="19" t="inlineStr">
+        <is>
+          <t>1:38:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>FAST GRIND 소계</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="14" t="n">
-        <v>25</v>
-      </c>
-      <c r="J5" s="14" t="n">
-        <v>5900</v>
-      </c>
-      <c r="K5" s="13" t="inlineStr">
-        <is>
-          <t>1:38:20</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="15" t="n"/>
+      <c r="H8" s="15" t="n"/>
+      <c r="I8" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="J8" s="16" t="n">
+        <v>13686</v>
+      </c>
+      <c r="K8" s="15" t="inlineStr">
+        <is>
+          <t>3:48:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>■ GX7</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="B8" s="21" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>형상</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>날수(F)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>날경(Ø)</t>
         </is>
       </c>
-      <c r="E8" s="21" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>상크경(Ø)</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>코팅</t>
         </is>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>특이사항</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t>완료</t>
         </is>
       </c>
-      <c r="I8" s="21" t="inlineStr">
+      <c r="I11" s="23" t="inlineStr">
         <is>
           <t>수량(개)</t>
         </is>
       </c>
-      <c r="J8" s="21" t="inlineStr">
+      <c r="J11" s="23" t="inlineStr">
         <is>
           <t>시간합계(초)</t>
         </is>
       </c>
-      <c r="K8" s="21" t="inlineStr">
+      <c r="K11" s="23" t="inlineStr">
         <is>
           <t>시간(H:M:S)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="22" t="n">
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>볼</t>
         </is>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C12" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D12" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="E12" s="24" t="n">
         <v>12</v>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F12" s="25" t="inlineStr">
         <is>
           <t>뮤</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t>0179</t>
         </is>
       </c>
-      <c r="H9" s="22" t="inlineStr"/>
-      <c r="I9" s="24" t="n">
+      <c r="H12" s="24" t="inlineStr"/>
+      <c r="I12" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="J9" s="24" t="n">
+      <c r="J12" s="26" t="n">
         <v>6225</v>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K12" s="24" t="inlineStr">
         <is>
           <t>1:43:45</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>볼</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" s="25" t="inlineStr">
+        <is>
+          <t>알파</t>
+        </is>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
+        <is>
+          <t>0118</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr"/>
+      <c r="I13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" s="26" t="n">
+        <v>1245</v>
+      </c>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>0:20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>R0.5</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="E14" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" s="25" t="inlineStr">
+        <is>
+          <t>알파</t>
+        </is>
+      </c>
+      <c r="G14" s="25" t="inlineStr">
+        <is>
+          <t>0118</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr"/>
+      <c r="I14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="26" t="n">
+        <v>255</v>
+      </c>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>0:04:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>평</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="E15" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" s="25" t="inlineStr">
+        <is>
+          <t>비</t>
+        </is>
+      </c>
+      <c r="G15" s="25" t="inlineStr">
+        <is>
+          <t>0179</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr"/>
+      <c r="I15" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="J15" s="26" t="n">
+        <v>3859</v>
+      </c>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>1:04:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>GX7 소계</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="13" t="n"/>
-      <c r="I10" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="J10" s="14" t="n">
-        <v>6225</v>
-      </c>
-      <c r="K10" s="13" t="inlineStr">
-        <is>
-          <t>1:43:45</t>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="15" t="n"/>
+      <c r="H16" s="15" t="n"/>
+      <c r="I16" s="16" t="n">
+        <v>36</v>
+      </c>
+      <c r="J16" s="16" t="n">
+        <v>11584</v>
+      </c>
+      <c r="K16" s="15" t="inlineStr">
+        <is>
+          <t>3:13:04</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A7:K7"/>
-    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A16:H16"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A5:H5"/>
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A8:H8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
